--- a/docs/vertical-packs/skills/doc-studio/samples/S2-数据工作簿.xlsx
+++ b/docs/vertical-packs/skills/doc-studio/samples/S2-数据工作簿.xlsx
@@ -228,9 +228,9 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2700000"/>
@@ -581,7 +581,7 @@
         <v>512</v>
       </c>
       <c r="D2">
-        <f>(B1-C1)/B1</f>
+        <f>(B2-C2)/B2</f>
         <v/>
       </c>
     </row>
@@ -598,7 +598,7 @@
         <v>530</v>
       </c>
       <c r="D3">
-        <f>(B2-C2)/B2</f>
+        <f>(B3-C3)/B3</f>
         <v/>
       </c>
     </row>
@@ -615,7 +615,7 @@
         <v>570</v>
       </c>
       <c r="D4">
-        <f>(B3-C3)/B3</f>
+        <f>(B4-C4)/B4</f>
         <v/>
       </c>
     </row>
@@ -632,7 +632,7 @@
         <v>601</v>
       </c>
       <c r="D5">
-        <f>(B4-C4)/B4</f>
+        <f>(B5-C5)/B5</f>
         <v/>
       </c>
     </row>
@@ -649,7 +649,7 @@
         <v>628</v>
       </c>
       <c r="D6">
-        <f>(B5-C5)/B5</f>
+        <f>(B6-C6)/B6</f>
         <v/>
       </c>
     </row>
@@ -666,7 +666,7 @@
         <v>650</v>
       </c>
       <c r="D7">
-        <f>(B6-C6)/B6</f>
+        <f>(B7-C7)/B7</f>
         <v/>
       </c>
     </row>
